--- a/144/DQ Templates and Instructions/Topic 5 DQ 1/Topic 5 DQ 1.xlsx
+++ b/144/DQ Templates and Instructions/Topic 5 DQ 1/Topic 5 DQ 1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gcumail.sharepoint.com/sites/MathematicsProgramFacultyStaff-MATOFTF/Shared Documents/MATOFTF/ALEKS/DQ Templates and Instructions/Topic 5 DQ 1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C765DE1B-BF38-4A4C-AC08-A10CA29FAE57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="46" documentId="8_{C765DE1B-BF38-4A4C-AC08-A10CA29FAE57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4661293C-8AB8-43BB-BF4D-41494D982289}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="12852" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Goals and Instructions" sheetId="6" r:id="rId1"/>
@@ -42,6 +42,24 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>tc={F7ECB685-58BD-4FCE-AAF0-B59A9D83EAD2}</author>
+  </authors>
+  <commentList>
+    <comment ref="M3" authorId="0" shapeId="0" xr:uid="{F7ECB685-58BD-4FCE-AAF0-B59A9D83EAD2}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    https://www.loom.com/share/3db320c2754a40c185a5970e0b1d0fa4</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
 <metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
@@ -65,7 +83,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="541" uniqueCount="515">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="543" uniqueCount="516">
   <si>
     <t>Excel Skills Learned</t>
   </si>
@@ -1909,12 +1927,15 @@
   <si>
     <t>Your Name Here</t>
   </si>
+  <si>
+    <t>Video</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="19">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2051,6 +2072,28 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="11">
@@ -2797,10 +2840,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="152">
+  <cellXfs count="153">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
       <protection locked="0"/>
@@ -3047,36 +3091,8 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="1" fontId="6" fillId="5" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="5" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="5" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="5" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="5" borderId="36" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -3365,11 +3381,63 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="51" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="36" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="8">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF00B050"/>
+      </font>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -3395,25 +3463,6 @@
         <i val="0"/>
         <color rgb="FF00B050"/>
       </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FF00B050"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
     </dxf>
     <dxf>
       <font>
@@ -3508,6 +3557,12 @@
     <xdr:clientData/>
   </xdr:oneCellAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <person displayName="Richard Ketchersid" id="{7D8657E4-A046-4CF8-B32F-309FF86895A0}" userId="S::richard.ketchersid@gcu.edu::a14ec2f7-27bd-40c3-90d9-209834cdef57" providerId="AD"/>
+</personList>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3805,6 +3860,20 @@
 </a:theme>
 </file>
 
+<file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="M3" dT="2026-07-16T19:53:52.72" personId="{7D8657E4-A046-4CF8-B32F-309FF86895A0}" id="{F7ECB685-58BD-4FCE-AAF0-B59A9D83EAD2}">
+    <text>https://www.loom.com/share/3db320c2754a40c185a5970e0b1d0fa4</text>
+    <extLst>
+      <x:ext xmlns:xltc2="http://schemas.microsoft.com/office/spreadsheetml/2020/threadedcomments2" uri="{F7C98A9C-CBB3-438F-8F68-D28B6AF4A901}">
+        <xltc2:checksum>1353146869</xltc2:checksum>
+        <xltc2:hyperlink startIndex="0" length="59" url="https://www.loom.com/share/3db320c2754a40c185a5970e0b1d0fa4"/>
+      </x:ext>
+    </extLst>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7225D041-BD6A-4E23-AE8C-8F9A4C0602AC}">
   <dimension ref="B2:I16"/>
@@ -3818,138 +3887,138 @@
       <c r="B3" s="30" t="s">
         <v>0</v>
       </c>
-      <c r="D3" s="80" t="s">
-        <v>1</v>
-      </c>
-      <c r="E3" s="81"/>
-      <c r="F3" s="81"/>
-      <c r="G3" s="81"/>
-      <c r="H3" s="81"/>
-      <c r="I3" s="82"/>
+      <c r="D3" s="73" t="s">
+        <v>1</v>
+      </c>
+      <c r="E3" s="74"/>
+      <c r="F3" s="74"/>
+      <c r="G3" s="74"/>
+      <c r="H3" s="74"/>
+      <c r="I3" s="75"/>
     </row>
     <row r="4" spans="2:9">
       <c r="B4" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="83"/>
-      <c r="E4" s="84"/>
-      <c r="F4" s="84"/>
-      <c r="G4" s="84"/>
-      <c r="H4" s="84"/>
-      <c r="I4" s="85"/>
+      <c r="D4" s="76"/>
+      <c r="E4" s="77"/>
+      <c r="F4" s="77"/>
+      <c r="G4" s="77"/>
+      <c r="H4" s="77"/>
+      <c r="I4" s="78"/>
     </row>
     <row r="5" spans="2:9" ht="30">
       <c r="B5" s="31" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="83"/>
-      <c r="E5" s="84"/>
-      <c r="F5" s="84"/>
-      <c r="G5" s="84"/>
-      <c r="H5" s="84"/>
-      <c r="I5" s="85"/>
+      <c r="D5" s="76"/>
+      <c r="E5" s="77"/>
+      <c r="F5" s="77"/>
+      <c r="G5" s="77"/>
+      <c r="H5" s="77"/>
+      <c r="I5" s="78"/>
     </row>
     <row r="6" spans="2:9">
       <c r="B6" s="31" t="s">
         <v>4</v>
       </c>
-      <c r="D6" s="83"/>
-      <c r="E6" s="84"/>
-      <c r="F6" s="84"/>
-      <c r="G6" s="84"/>
-      <c r="H6" s="84"/>
-      <c r="I6" s="85"/>
+      <c r="D6" s="76"/>
+      <c r="E6" s="77"/>
+      <c r="F6" s="77"/>
+      <c r="G6" s="77"/>
+      <c r="H6" s="77"/>
+      <c r="I6" s="78"/>
     </row>
     <row r="7" spans="2:9" ht="15.75" thickBot="1">
       <c r="B7" s="31"/>
-      <c r="D7" s="86"/>
-      <c r="E7" s="87"/>
-      <c r="F7" s="87"/>
-      <c r="G7" s="87"/>
-      <c r="H7" s="87"/>
-      <c r="I7" s="88"/>
+      <c r="D7" s="79"/>
+      <c r="E7" s="80"/>
+      <c r="F7" s="80"/>
+      <c r="G7" s="80"/>
+      <c r="H7" s="80"/>
+      <c r="I7" s="81"/>
     </row>
     <row r="8" spans="2:9" ht="15.75" thickBot="1">
       <c r="B8" s="32"/>
     </row>
     <row r="9" spans="2:9" ht="15" customHeight="1" thickBot="1">
       <c r="B9" s="32"/>
-      <c r="D9" s="89" t="s">
+      <c r="D9" s="82" t="s">
         <v>5</v>
       </c>
-      <c r="E9" s="90"/>
-      <c r="F9" s="90"/>
-      <c r="G9" s="90"/>
-      <c r="H9" s="90"/>
-      <c r="I9" s="91"/>
+      <c r="E9" s="83"/>
+      <c r="F9" s="83"/>
+      <c r="G9" s="83"/>
+      <c r="H9" s="83"/>
+      <c r="I9" s="84"/>
     </row>
     <row r="10" spans="2:9" ht="15.75" thickBot="1">
       <c r="B10" s="30" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="92"/>
-      <c r="E10" s="93"/>
-      <c r="F10" s="93"/>
-      <c r="G10" s="93"/>
-      <c r="H10" s="93"/>
-      <c r="I10" s="94"/>
+      <c r="D10" s="85"/>
+      <c r="E10" s="86"/>
+      <c r="F10" s="86"/>
+      <c r="G10" s="86"/>
+      <c r="H10" s="86"/>
+      <c r="I10" s="87"/>
     </row>
     <row r="11" spans="2:9" ht="30">
       <c r="B11" s="31" t="s">
         <v>7</v>
       </c>
-      <c r="D11" s="92"/>
-      <c r="E11" s="93"/>
-      <c r="F11" s="93"/>
-      <c r="G11" s="93"/>
-      <c r="H11" s="93"/>
-      <c r="I11" s="94"/>
+      <c r="D11" s="85"/>
+      <c r="E11" s="86"/>
+      <c r="F11" s="86"/>
+      <c r="G11" s="86"/>
+      <c r="H11" s="86"/>
+      <c r="I11" s="87"/>
     </row>
     <row r="12" spans="2:9">
       <c r="B12" s="31" t="s">
         <v>8</v>
       </c>
-      <c r="D12" s="92"/>
-      <c r="E12" s="93"/>
-      <c r="F12" s="93"/>
-      <c r="G12" s="93"/>
-      <c r="H12" s="93"/>
-      <c r="I12" s="94"/>
+      <c r="D12" s="85"/>
+      <c r="E12" s="86"/>
+      <c r="F12" s="86"/>
+      <c r="G12" s="86"/>
+      <c r="H12" s="86"/>
+      <c r="I12" s="87"/>
     </row>
     <row r="13" spans="2:9">
       <c r="B13" s="32" t="s">
         <v>9</v>
       </c>
-      <c r="D13" s="92"/>
-      <c r="E13" s="93"/>
-      <c r="F13" s="93"/>
-      <c r="G13" s="93"/>
-      <c r="H13" s="93"/>
-      <c r="I13" s="94"/>
+      <c r="D13" s="85"/>
+      <c r="E13" s="86"/>
+      <c r="F13" s="86"/>
+      <c r="G13" s="86"/>
+      <c r="H13" s="86"/>
+      <c r="I13" s="87"/>
     </row>
     <row r="14" spans="2:9">
-      <c r="D14" s="92"/>
-      <c r="E14" s="93"/>
-      <c r="F14" s="93"/>
-      <c r="G14" s="93"/>
-      <c r="H14" s="93"/>
-      <c r="I14" s="94"/>
+      <c r="D14" s="85"/>
+      <c r="E14" s="86"/>
+      <c r="F14" s="86"/>
+      <c r="G14" s="86"/>
+      <c r="H14" s="86"/>
+      <c r="I14" s="87"/>
     </row>
     <row r="15" spans="2:9">
-      <c r="D15" s="92"/>
-      <c r="E15" s="93"/>
-      <c r="F15" s="93"/>
-      <c r="G15" s="93"/>
-      <c r="H15" s="93"/>
-      <c r="I15" s="94"/>
+      <c r="D15" s="85"/>
+      <c r="E15" s="86"/>
+      <c r="F15" s="86"/>
+      <c r="G15" s="86"/>
+      <c r="H15" s="86"/>
+      <c r="I15" s="87"/>
     </row>
     <row r="16" spans="2:9" ht="15.75" thickBot="1">
-      <c r="D16" s="95"/>
-      <c r="E16" s="96"/>
-      <c r="F16" s="96"/>
-      <c r="G16" s="96"/>
-      <c r="H16" s="96"/>
-      <c r="I16" s="97"/>
+      <c r="D16" s="88"/>
+      <c r="E16" s="89"/>
+      <c r="F16" s="89"/>
+      <c r="G16" s="89"/>
+      <c r="H16" s="89"/>
+      <c r="I16" s="90"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -3961,7 +4030,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="C1:Z120"/>
   <sheetFormatPr defaultColWidth="9.28515625" defaultRowHeight="15"/>
   <cols>
@@ -3995,23 +4064,23 @@
       <c r="F1" s="1"/>
     </row>
     <row r="2" spans="3:26" ht="69.599999999999994" customHeight="1" thickBot="1">
-      <c r="C2" s="108" t="s">
+      <c r="C2" s="101" t="s">
         <v>498</v>
       </c>
-      <c r="D2" s="109"/>
+      <c r="D2" s="102"/>
       <c r="E2" s="59" t="s">
         <v>514</v>
       </c>
-      <c r="F2" s="110" t="s">
+      <c r="F2" s="103" t="s">
         <v>10</v>
       </c>
-      <c r="G2" s="111"/>
-      <c r="H2" s="111"/>
-      <c r="I2" s="111"/>
-      <c r="J2" s="111"/>
-      <c r="K2" s="111"/>
-      <c r="L2" s="111"/>
-      <c r="M2" s="111"/>
+      <c r="G2" s="104"/>
+      <c r="H2" s="104"/>
+      <c r="I2" s="104"/>
+      <c r="J2" s="104"/>
+      <c r="K2" s="104"/>
+      <c r="L2" s="104"/>
+      <c r="M2" s="104"/>
       <c r="N2" s="16"/>
       <c r="O2" s="16"/>
       <c r="P2" s="16"/>
@@ -4039,13 +4108,16 @@
         <v>14</v>
       </c>
       <c r="G3" s="25"/>
-      <c r="H3" s="108" t="s">
+      <c r="H3" s="101" t="s">
         <v>497</v>
       </c>
-      <c r="I3" s="103"/>
-      <c r="J3" s="103"/>
-      <c r="K3" s="104"/>
-      <c r="N3" s="16"/>
+      <c r="I3" s="96"/>
+      <c r="J3" s="96"/>
+      <c r="K3" s="97"/>
+      <c r="M3" s="145" t="s">
+        <v>515</v>
+      </c>
+      <c r="N3" s="145"/>
       <c r="O3" s="16"/>
       <c r="P3" s="16"/>
       <c r="Q3" s="16"/>
@@ -4070,11 +4142,11 @@
         <f>IF(E$2="Your Name Here", "Enter your name",ROUND(_xlfn.NORM.INV(Random!D120,20,3),0))</f>
         <v>Enter your name</v>
       </c>
-      <c r="F4" s="65"/>
-      <c r="H4" s="112"/>
-      <c r="I4" s="113"/>
-      <c r="J4" s="113"/>
-      <c r="K4" s="114"/>
+      <c r="F4" s="149"/>
+      <c r="H4" s="105"/>
+      <c r="I4" s="106"/>
+      <c r="J4" s="106"/>
+      <c r="K4" s="107"/>
       <c r="L4" s="6"/>
       <c r="M4" s="6"/>
       <c r="N4" s="3"/>
@@ -4091,16 +4163,16 @@
         <f>IF(E$2="Your Name Here", "Enter your name",ROUND(_xlfn.NORM.INV(Random!D121,20,3),0))</f>
         <v>Enter your name</v>
       </c>
-      <c r="F5" s="65"/>
-      <c r="H5" s="112"/>
-      <c r="I5" s="113"/>
-      <c r="J5" s="113"/>
-      <c r="K5" s="114"/>
+      <c r="F5" s="149"/>
+      <c r="H5" s="105"/>
+      <c r="I5" s="106"/>
+      <c r="J5" s="106"/>
+      <c r="K5" s="107"/>
       <c r="L5" s="6"/>
-      <c r="M5" s="117" t="s">
+      <c r="M5" s="110" t="s">
         <v>15</v>
       </c>
-      <c r="N5" s="118"/>
+      <c r="N5" s="111"/>
       <c r="O5" s="16"/>
       <c r="P5" s="16"/>
       <c r="Q5" s="16"/>
@@ -4125,11 +4197,11 @@
         <f>IF(E$2="Your Name Here", "Enter your name",ROUND(_xlfn.NORM.INV(Random!D122,20,3),0))</f>
         <v>Enter your name</v>
       </c>
-      <c r="F6" s="65"/>
-      <c r="H6" s="112"/>
-      <c r="I6" s="113"/>
-      <c r="J6" s="113"/>
-      <c r="K6" s="114"/>
+      <c r="F6" s="149"/>
+      <c r="H6" s="105"/>
+      <c r="I6" s="106"/>
+      <c r="J6" s="106"/>
+      <c r="K6" s="107"/>
       <c r="L6" s="6"/>
       <c r="M6" s="38" t="s">
         <v>16</v>
@@ -4161,11 +4233,11 @@
         <f>IF(E$2="Your Name Here", "Enter your name",ROUND(_xlfn.NORM.INV(Random!D123,20,3),0))</f>
         <v>Enter your name</v>
       </c>
-      <c r="F7" s="65"/>
-      <c r="H7" s="105"/>
-      <c r="I7" s="113"/>
-      <c r="J7" s="113"/>
-      <c r="K7" s="114"/>
+      <c r="F7" s="149"/>
+      <c r="H7" s="98"/>
+      <c r="I7" s="106"/>
+      <c r="J7" s="106"/>
+      <c r="K7" s="107"/>
       <c r="M7" s="40" t="s">
         <v>18</v>
       </c>
@@ -4196,7 +4268,7 @@
         <f>IF(E$2="Your Name Here", "Enter your name",ROUND(_xlfn.NORM.INV(Random!D124,20,3),0))</f>
         <v>Enter your name</v>
       </c>
-      <c r="F8" s="65"/>
+      <c r="F8" s="149"/>
       <c r="H8" s="9"/>
       <c r="I8" s="10" t="s">
         <v>20</v>
@@ -4235,13 +4307,13 @@
         <f>IF(E$2="Your Name Here", "Enter your name",ROUND(_xlfn.NORM.INV(Random!D125,20,3),0))</f>
         <v>Enter your name</v>
       </c>
-      <c r="F9" s="65"/>
+      <c r="F9" s="149"/>
       <c r="H9" s="52" t="s">
         <v>25</v>
       </c>
-      <c r="I9" s="70"/>
-      <c r="J9" s="70"/>
-      <c r="K9" s="70"/>
+      <c r="I9" s="146"/>
+      <c r="J9" s="146"/>
+      <c r="K9" s="146"/>
       <c r="M9" s="8" t="s">
         <v>26</v>
       </c>
@@ -4270,13 +4342,13 @@
         <f>IF(E$2="Your Name Here", "Enter your name",ROUND(_xlfn.NORM.INV(Random!D126,20,3),0))</f>
         <v>Enter your name</v>
       </c>
-      <c r="F10" s="65"/>
+      <c r="F10" s="149"/>
       <c r="H10" s="53" t="s">
         <v>28</v>
       </c>
-      <c r="I10" s="71"/>
-      <c r="J10" s="71"/>
-      <c r="K10" s="71"/>
+      <c r="I10" s="147"/>
+      <c r="J10" s="147"/>
+      <c r="K10" s="147"/>
       <c r="M10" s="43" t="s">
         <v>29</v>
       </c>
@@ -4305,13 +4377,13 @@
         <f>IF(E$2="Your Name Here", "Enter your name",ROUND(_xlfn.NORM.INV(Random!D127,20,3),0))</f>
         <v>Enter your name</v>
       </c>
-      <c r="F11" s="65"/>
+      <c r="F11" s="149"/>
       <c r="H11" s="53" t="s">
         <v>31</v>
       </c>
-      <c r="I11" s="66"/>
-      <c r="J11" s="66"/>
-      <c r="K11" s="66"/>
+      <c r="I11" s="147"/>
+      <c r="J11" s="147"/>
+      <c r="K11" s="147"/>
       <c r="N11" s="16"/>
       <c r="O11" s="16"/>
       <c r="P11" s="16"/>
@@ -4335,22 +4407,22 @@
         <f>IF(E$2="Your Name Here", "Enter your name",ROUND(_xlfn.NORM.INV(Random!D128,20,3),0))</f>
         <v>Enter your name</v>
       </c>
-      <c r="F12" s="65"/>
+      <c r="F12" s="149"/>
       <c r="H12" s="54" t="s">
         <v>32</v>
       </c>
-      <c r="I12" s="72"/>
-      <c r="J12" s="72"/>
-      <c r="K12" s="72"/>
+      <c r="I12" s="148"/>
+      <c r="J12" s="148"/>
+      <c r="K12" s="148"/>
       <c r="M12" s="45">
         <v>15</v>
       </c>
-      <c r="N12" s="121" t="s">
+      <c r="N12" s="114" t="s">
         <v>33</v>
       </c>
-      <c r="O12" s="121"/>
-      <c r="P12" s="121"/>
-      <c r="Q12" s="122"/>
+      <c r="O12" s="114"/>
+      <c r="P12" s="114"/>
+      <c r="Q12" s="115"/>
       <c r="R12" s="16"/>
       <c r="S12" s="16"/>
       <c r="T12" s="16"/>
@@ -4370,16 +4442,16 @@
         <f>IF(E$2="Your Name Here", "Enter your name",ROUND(_xlfn.NORM.INV(Random!D129,20,3),0))</f>
         <v>Enter your name</v>
       </c>
-      <c r="F13" s="65"/>
+      <c r="F13" s="149"/>
       <c r="M13" s="46">
         <v>15</v>
       </c>
-      <c r="N13" s="119" t="s">
+      <c r="N13" s="112" t="s">
         <v>34</v>
       </c>
-      <c r="O13" s="119"/>
-      <c r="P13" s="119"/>
-      <c r="Q13" s="120"/>
+      <c r="O13" s="112"/>
+      <c r="P13" s="112"/>
+      <c r="Q13" s="113"/>
       <c r="R13" s="16"/>
       <c r="S13" s="16"/>
       <c r="T13" s="16"/>
@@ -4399,16 +4471,16 @@
         <f>IF(E$2="Your Name Here", "Enter your name",ROUND(_xlfn.NORM.INV(Random!D130,20,3),0))</f>
         <v>Enter your name</v>
       </c>
-      <c r="F14" s="65"/>
+      <c r="F14" s="149"/>
       <c r="M14" s="47">
         <v>16</v>
       </c>
-      <c r="N14" s="123" t="s">
+      <c r="N14" s="116" t="s">
         <v>35</v>
       </c>
-      <c r="O14" s="123"/>
-      <c r="P14" s="123"/>
-      <c r="Q14" s="124"/>
+      <c r="O14" s="116"/>
+      <c r="P14" s="116"/>
+      <c r="Q14" s="117"/>
     </row>
     <row r="15" spans="3:26" ht="20.100000000000001" customHeight="1" thickBot="1">
       <c r="C15" s="22">
@@ -4422,23 +4494,23 @@
         <f>IF(E$2="Your Name Here", "Enter your name",ROUND(_xlfn.NORM.INV(Random!D131,20,3),0))</f>
         <v>Enter your name</v>
       </c>
-      <c r="F15" s="65"/>
-      <c r="H15" s="108" t="s">
+      <c r="F15" s="149"/>
+      <c r="H15" s="101" t="s">
         <v>496</v>
       </c>
-      <c r="I15" s="103"/>
-      <c r="J15" s="103"/>
-      <c r="K15" s="104"/>
+      <c r="I15" s="96"/>
+      <c r="J15" s="96"/>
+      <c r="K15" s="97"/>
       <c r="L15" s="16"/>
       <c r="M15" s="48">
         <v>16</v>
       </c>
-      <c r="N15" s="125" t="s">
+      <c r="N15" s="118" t="s">
         <v>37</v>
       </c>
-      <c r="O15" s="125"/>
-      <c r="P15" s="125"/>
-      <c r="Q15" s="126"/>
+      <c r="O15" s="118"/>
+      <c r="P15" s="118"/>
+      <c r="Q15" s="119"/>
       <c r="R15" s="16"/>
       <c r="S15" s="16"/>
       <c r="T15" s="16"/>
@@ -4458,11 +4530,11 @@
         <f>IF(E$2="Your Name Here", "Enter your name",ROUND(_xlfn.NORM.INV(Random!D132,20,3),0))</f>
         <v>Enter your name</v>
       </c>
-      <c r="F16" s="65"/>
-      <c r="H16" s="112"/>
-      <c r="I16" s="113"/>
-      <c r="J16" s="113"/>
-      <c r="K16" s="114"/>
+      <c r="F16" s="149"/>
+      <c r="H16" s="105"/>
+      <c r="I16" s="106"/>
+      <c r="J16" s="106"/>
+      <c r="K16" s="107"/>
       <c r="L16" s="16"/>
       <c r="M16" s="16"/>
       <c r="N16" s="16"/>
@@ -4488,11 +4560,11 @@
         <f>IF(E$2="Your Name Here", "Enter your name",ROUND(_xlfn.NORM.INV(Random!D133,20,3),0))</f>
         <v>Enter your name</v>
       </c>
-      <c r="F17" s="65"/>
-      <c r="H17" s="112"/>
-      <c r="I17" s="113"/>
-      <c r="J17" s="106"/>
-      <c r="K17" s="107"/>
+      <c r="F17" s="149"/>
+      <c r="H17" s="105"/>
+      <c r="I17" s="106"/>
+      <c r="J17" s="99"/>
+      <c r="K17" s="100"/>
       <c r="L17" s="16"/>
       <c r="M17" s="16"/>
       <c r="N17" s="16"/>
@@ -4518,11 +4590,11 @@
         <f>IF(E$2="Your Name Here", "Enter your name",ROUND(_xlfn.NORM.INV(Random!D134,20,3),0))</f>
         <v>Enter your name</v>
       </c>
-      <c r="F18" s="65"/>
-      <c r="H18" s="115" t="s">
+      <c r="F18" s="149"/>
+      <c r="H18" s="108" t="s">
         <v>38</v>
       </c>
-      <c r="I18" s="116"/>
+      <c r="I18" s="109"/>
       <c r="J18" s="18"/>
       <c r="K18" s="18"/>
       <c r="L18" s="16"/>
@@ -4550,15 +4622,15 @@
         <f>IF(E$2="Your Name Here", "Enter your name",ROUND(_xlfn.NORM.INV(Random!D135,20,3),0))</f>
         <v>Enter your name</v>
       </c>
-      <c r="F19" s="65"/>
+      <c r="F19" s="149"/>
       <c r="H19" s="60" t="s">
         <v>39</v>
       </c>
-      <c r="I19" s="67"/>
-      <c r="J19" s="98" t="s">
+      <c r="I19" s="150"/>
+      <c r="J19" s="91" t="s">
         <v>40</v>
       </c>
-      <c r="K19" s="99"/>
+      <c r="K19" s="92"/>
       <c r="L19" s="16"/>
       <c r="M19" s="16"/>
       <c r="N19" s="16"/>
@@ -4584,13 +4656,13 @@
         <f>IF(E$2="Your Name Here", "Enter your name",ROUND(_xlfn.NORM.INV(Random!D136,20,3),0))</f>
         <v>Enter your name</v>
       </c>
-      <c r="F20" s="65"/>
+      <c r="F20" s="149"/>
       <c r="H20" s="20" t="s">
         <v>41</v>
       </c>
-      <c r="I20" s="68"/>
-      <c r="J20" s="100"/>
-      <c r="K20" s="101"/>
+      <c r="I20" s="151"/>
+      <c r="J20" s="93"/>
+      <c r="K20" s="94"/>
     </row>
     <row r="21" spans="3:25" ht="20.100000000000001" customHeight="1">
       <c r="C21" s="22">
@@ -4604,7 +4676,7 @@
         <f>IF(E$2="Your Name Here", "Enter your name",ROUND(_xlfn.NORM.INV(Random!D137,20,3),0))</f>
         <v>Enter your name</v>
       </c>
-      <c r="F21" s="65"/>
+      <c r="F21" s="149"/>
       <c r="H21" s="18"/>
       <c r="I21" s="18"/>
       <c r="J21" s="18"/>
@@ -4636,7 +4708,7 @@
         <f>IF(E$2="Your Name Here", "Enter your name",ROUND(_xlfn.NORM.INV(Random!D138,20,3),0))</f>
         <v>Enter your name</v>
       </c>
-      <c r="F22" s="65"/>
+      <c r="F22" s="149"/>
       <c r="H22" s="17"/>
       <c r="I22" s="17"/>
       <c r="J22" s="17"/>
@@ -4664,7 +4736,7 @@
         <f>IF(E$2="Your Name Here", "Enter your name",ROUND(_xlfn.NORM.INV(Random!D139,20,3),0))</f>
         <v>Enter your name</v>
       </c>
-      <c r="F23" s="65"/>
+      <c r="F23" s="149"/>
       <c r="H23" s="17"/>
       <c r="I23" s="17"/>
       <c r="J23" s="17"/>
@@ -4692,7 +4764,7 @@
         <f>IF(E$2="Your Name Here", "Enter your name",ROUND(_xlfn.NORM.INV(Random!D140,20,3),0))</f>
         <v>Enter your name</v>
       </c>
-      <c r="F24" s="65"/>
+      <c r="F24" s="149"/>
       <c r="H24" s="17"/>
       <c r="I24" s="17"/>
       <c r="J24" s="17"/>
@@ -4720,18 +4792,18 @@
         <f>IF(E$2="Your Name Here", "Enter your name",ROUND(_xlfn.NORM.INV(Random!D141,20,3),0))</f>
         <v>Enter your name</v>
       </c>
-      <c r="F25" s="65"/>
-      <c r="H25" s="102" t="s">
+      <c r="F25" s="149"/>
+      <c r="H25" s="95" t="s">
         <v>510</v>
       </c>
-      <c r="I25" s="103"/>
-      <c r="J25" s="103"/>
-      <c r="K25" s="103"/>
-      <c r="L25" s="103"/>
-      <c r="M25" s="103"/>
-      <c r="N25" s="103"/>
-      <c r="O25" s="103"/>
-      <c r="P25" s="104"/>
+      <c r="I25" s="96"/>
+      <c r="J25" s="96"/>
+      <c r="K25" s="96"/>
+      <c r="L25" s="96"/>
+      <c r="M25" s="96"/>
+      <c r="N25" s="96"/>
+      <c r="O25" s="96"/>
+      <c r="P25" s="97"/>
       <c r="Q25" s="17"/>
       <c r="R25" s="17"/>
       <c r="S25" s="17"/>
@@ -4750,16 +4822,16 @@
         <f>IF(E$2="Your Name Here", "Enter your name",ROUND(_xlfn.NORM.INV(Random!D142,20,3),0))</f>
         <v>Enter your name</v>
       </c>
-      <c r="F26" s="65"/>
-      <c r="H26" s="105"/>
-      <c r="I26" s="106"/>
-      <c r="J26" s="106"/>
-      <c r="K26" s="106"/>
-      <c r="L26" s="106"/>
-      <c r="M26" s="106"/>
-      <c r="N26" s="106"/>
-      <c r="O26" s="106"/>
-      <c r="P26" s="107"/>
+      <c r="F26" s="149"/>
+      <c r="H26" s="98"/>
+      <c r="I26" s="99"/>
+      <c r="J26" s="99"/>
+      <c r="K26" s="99"/>
+      <c r="L26" s="99"/>
+      <c r="M26" s="99"/>
+      <c r="N26" s="99"/>
+      <c r="O26" s="99"/>
+      <c r="P26" s="100"/>
       <c r="Q26" s="17"/>
       <c r="R26" s="17"/>
       <c r="S26" s="17"/>
@@ -4782,7 +4854,7 @@
         <f>IF(E$2="Your Name Here", "Enter your name",ROUND(_xlfn.NORM.INV(Random!D143,20,3),0))</f>
         <v>Enter your name</v>
       </c>
-      <c r="F27" s="65"/>
+      <c r="F27" s="149"/>
       <c r="H27" s="61"/>
       <c r="I27" s="61" t="s">
         <v>508</v>
@@ -4818,7 +4890,7 @@
         <f>IF(E$2="Your Name Here", "Enter your name",ROUND(_xlfn.NORM.INV(Random!D144,20,3),0))</f>
         <v>Enter your name</v>
       </c>
-      <c r="F28" s="65"/>
+      <c r="F28" s="149"/>
       <c r="H28" s="62" t="s">
         <v>501</v>
       </c>
@@ -4826,15 +4898,17 @@
       <c r="J28" s="63" t="s">
         <v>511</v>
       </c>
-      <c r="K28" s="57"/>
+      <c r="K28" s="57" t="s">
+        <v>512</v>
+      </c>
       <c r="L28" s="63" t="s">
         <v>503</v>
       </c>
-      <c r="M28" s="73"/>
+      <c r="M28" s="152"/>
       <c r="N28" s="63" t="s">
         <v>505</v>
       </c>
-      <c r="O28" s="73"/>
+      <c r="O28" s="152"/>
       <c r="P28" s="64" t="s">
         <v>507</v>
       </c>
@@ -4856,7 +4930,7 @@
         <f>IF(E$2="Your Name Here", "Enter your name",ROUND(_xlfn.NORM.INV(Random!D145,20,3),0))</f>
         <v>Enter your name</v>
       </c>
-      <c r="F29" s="65"/>
+      <c r="F29" s="149"/>
       <c r="H29" s="55"/>
       <c r="J29" s="56"/>
       <c r="K29" s="56" t="s">
@@ -4883,7 +4957,7 @@
         <f>IF(E$2="Your Name Here", "Enter your name",ROUND(_xlfn.NORM.INV(Random!D146,20,3),0))</f>
         <v>Enter your name</v>
       </c>
-      <c r="F30" s="65"/>
+      <c r="F30" s="149"/>
       <c r="H30" s="55"/>
       <c r="I30" s="56"/>
       <c r="J30" s="56"/>
@@ -4913,7 +4987,7 @@
         <f>IF(E$2="Your Name Here", "Enter your name",ROUND(_xlfn.NORM.INV(Random!D147,20,3),0))</f>
         <v>Enter your name</v>
       </c>
-      <c r="F31" s="65"/>
+      <c r="F31" s="149"/>
       <c r="K31" s="22" t="s">
         <v>513</v>
       </c>
@@ -4935,7 +5009,7 @@
         <f>IF(E$2="Your Name Here", "Enter your name",ROUND(_xlfn.NORM.INV(Random!D148,20,3),0))</f>
         <v>Enter your name</v>
       </c>
-      <c r="F32" s="65"/>
+      <c r="F32" s="149"/>
       <c r="Q32" s="17"/>
       <c r="R32" s="17"/>
       <c r="S32" s="17"/>
@@ -4954,8 +5028,8 @@
         <f>IF(E$2="Your Name Here", "Enter your name",ROUND(_xlfn.NORM.INV(Random!D149,20,3),0))</f>
         <v>Enter your name</v>
       </c>
-      <c r="F33" s="65"/>
-      <c r="H33" s="69"/>
+      <c r="F33" s="149"/>
+      <c r="H33" s="65"/>
       <c r="I33" s="51"/>
       <c r="J33" s="51"/>
       <c r="K33" s="51"/>
@@ -4977,7 +5051,7 @@
         <f>IF(E$2="Your Name Here", "Enter your name",ROUND(_xlfn.NORM.INV(Random!D150,20,3),0))</f>
         <v>Enter your name</v>
       </c>
-      <c r="F34" s="65"/>
+      <c r="F34" s="149"/>
     </row>
     <row r="35" spans="3:25" ht="20.100000000000001" customHeight="1">
       <c r="C35" s="22">
@@ -4991,7 +5065,7 @@
         <f>IF(E$2="Your Name Here", "Enter your name",ROUND(_xlfn.NORM.INV(Random!D151,20,3),0))</f>
         <v>Enter your name</v>
       </c>
-      <c r="F35" s="65"/>
+      <c r="F35" s="149"/>
     </row>
     <row r="36" spans="3:25" ht="20.100000000000001" customHeight="1">
       <c r="C36" s="22">
@@ -5005,7 +5079,7 @@
         <f>IF(E$2="Your Name Here", "Enter your name",ROUND(_xlfn.NORM.INV(Random!D152,20,3),0))</f>
         <v>Enter your name</v>
       </c>
-      <c r="F36" s="65"/>
+      <c r="F36" s="149"/>
       <c r="Q36" s="17"/>
       <c r="R36" s="17"/>
       <c r="S36" s="17"/>
@@ -5026,7 +5100,7 @@
         <f>IF(E$2="Your Name Here", "Enter your name",ROUND(_xlfn.NORM.INV(Random!D153,20,3),0))</f>
         <v>Enter your name</v>
       </c>
-      <c r="F37" s="65"/>
+      <c r="F37" s="149"/>
       <c r="J37" s="17"/>
       <c r="K37" s="17"/>
       <c r="L37" s="17"/>
@@ -5050,7 +5124,7 @@
         <f>IF(E$2="Your Name Here", "Enter your name",ROUND(_xlfn.NORM.INV(Random!D154,20,3),0))</f>
         <v>Enter your name</v>
       </c>
-      <c r="F38" s="65"/>
+      <c r="F38" s="149"/>
       <c r="J38" s="17"/>
       <c r="K38" s="17"/>
       <c r="L38" s="17"/>
@@ -5074,7 +5148,7 @@
         <f>IF(E$2="Your Name Here", "Enter your name",ROUND(_xlfn.NORM.INV(Random!D155,20,3),0))</f>
         <v>Enter your name</v>
       </c>
-      <c r="F39" s="65"/>
+      <c r="F39" s="149"/>
       <c r="J39" s="17"/>
       <c r="K39" s="17"/>
       <c r="L39" s="17"/>
@@ -5098,7 +5172,7 @@
         <f>IF(E$2="Your Name Here", "Enter your name",ROUND(_xlfn.NORM.INV(Random!D156,20,3),0))</f>
         <v>Enter your name</v>
       </c>
-      <c r="F40" s="65"/>
+      <c r="F40" s="149"/>
       <c r="J40" s="17"/>
       <c r="K40" s="17"/>
       <c r="L40" s="17"/>
@@ -5122,7 +5196,7 @@
         <f>IF(E$2="Your Name Here", "Enter your name",ROUND(_xlfn.NORM.INV(Random!D157,20,3),0))</f>
         <v>Enter your name</v>
       </c>
-      <c r="F41" s="65"/>
+      <c r="F41" s="149"/>
       <c r="J41" s="17"/>
       <c r="K41" s="17"/>
       <c r="L41" s="17"/>
@@ -5146,7 +5220,7 @@
         <f>IF(E$2="Your Name Here", "Enter your name",ROUND(_xlfn.NORM.INV(Random!D158,20,3),0))</f>
         <v>Enter your name</v>
       </c>
-      <c r="F42" s="65"/>
+      <c r="F42" s="149"/>
     </row>
     <row r="43" spans="3:25" ht="20.100000000000001" customHeight="1">
       <c r="C43" s="22">
@@ -5160,7 +5234,7 @@
         <f>IF(E$2="Your Name Here", "Enter your name",ROUND(_xlfn.NORM.INV(Random!D159,20,3),0))</f>
         <v>Enter your name</v>
       </c>
-      <c r="F43" s="65"/>
+      <c r="F43" s="149"/>
       <c r="J43" s="17"/>
       <c r="K43" s="17"/>
       <c r="L43" s="17"/>
@@ -5184,7 +5258,7 @@
         <f>IF(E$2="Your Name Here", "Enter your name",ROUND(_xlfn.NORM.INV(Random!D160,20,3),0))</f>
         <v>Enter your name</v>
       </c>
-      <c r="F44" s="65"/>
+      <c r="F44" s="149"/>
       <c r="J44" s="17"/>
       <c r="K44" s="17"/>
       <c r="L44" s="17"/>
@@ -5208,7 +5282,7 @@
         <f>IF(E$2="Your Name Here", "Enter your name",ROUND(_xlfn.NORM.INV(Random!D161,20,3),0))</f>
         <v>Enter your name</v>
       </c>
-      <c r="F45" s="65"/>
+      <c r="F45" s="149"/>
       <c r="J45" s="17"/>
       <c r="K45" s="17"/>
       <c r="L45" s="17"/>
@@ -5232,7 +5306,7 @@
         <f>IF(E$2="Your Name Here", "Enter your name",ROUND(_xlfn.NORM.INV(Random!D162,20,3),0))</f>
         <v>Enter your name</v>
       </c>
-      <c r="F46" s="65"/>
+      <c r="F46" s="149"/>
       <c r="J46" s="17"/>
       <c r="K46" s="17"/>
       <c r="L46" s="17"/>
@@ -5256,7 +5330,7 @@
         <f>IF(E$2="Your Name Here", "Enter your name",ROUND(_xlfn.NORM.INV(Random!D163,20,3),0))</f>
         <v>Enter your name</v>
       </c>
-      <c r="F47" s="65"/>
+      <c r="F47" s="149"/>
       <c r="J47" s="17"/>
       <c r="K47" s="17"/>
       <c r="L47" s="17"/>
@@ -5280,7 +5354,7 @@
         <f>IF(E$2="Your Name Here", "Enter your name",ROUND(_xlfn.NORM.INV(Random!D164,20,3),0))</f>
         <v>Enter your name</v>
       </c>
-      <c r="F48" s="65"/>
+      <c r="F48" s="149"/>
       <c r="J48" s="17"/>
       <c r="K48" s="17"/>
       <c r="L48" s="17"/>
@@ -5304,7 +5378,7 @@
         <f>IF(E$2="Your Name Here", "Enter your name",ROUND(_xlfn.NORM.INV(Random!D165,20,3),0))</f>
         <v>Enter your name</v>
       </c>
-      <c r="F49" s="65"/>
+      <c r="F49" s="149"/>
     </row>
     <row r="50" spans="3:6" ht="20.100000000000001" customHeight="1">
       <c r="C50" s="22">
@@ -5318,7 +5392,7 @@
         <f>IF(E$2="Your Name Here", "Enter your name",ROUND(_xlfn.NORM.INV(Random!D166,20,3),0))</f>
         <v>Enter your name</v>
       </c>
-      <c r="F50" s="65"/>
+      <c r="F50" s="149"/>
     </row>
     <row r="51" spans="3:6" ht="20.100000000000001" customHeight="1">
       <c r="C51" s="22">
@@ -5332,7 +5406,7 @@
         <f>IF(E$2="Your Name Here", "Enter your name",ROUND(_xlfn.NORM.INV(Random!D167,20,3),0))</f>
         <v>Enter your name</v>
       </c>
-      <c r="F51" s="65"/>
+      <c r="F51" s="149"/>
     </row>
     <row r="52" spans="3:6" ht="20.100000000000001" customHeight="1">
       <c r="C52" s="22">
@@ -5346,7 +5420,7 @@
         <f>IF(E$2="Your Name Here", "Enter your name",ROUND(_xlfn.NORM.INV(Random!D168,20,3),0))</f>
         <v>Enter your name</v>
       </c>
-      <c r="F52" s="65"/>
+      <c r="F52" s="149"/>
     </row>
     <row r="53" spans="3:6" ht="20.100000000000001" customHeight="1">
       <c r="C53" s="22">
@@ -5360,7 +5434,7 @@
         <f>IF(E$2="Your Name Here", "Enter your name",ROUND(_xlfn.NORM.INV(Random!D169,20,3),0))</f>
         <v>Enter your name</v>
       </c>
-      <c r="F53" s="65"/>
+      <c r="F53" s="149"/>
     </row>
     <row r="54" spans="3:6" ht="20.100000000000001" customHeight="1">
       <c r="C54" s="22">
@@ -5374,7 +5448,7 @@
         <f>IF(E$2="Your Name Here", "Enter your name",ROUND(_xlfn.NORM.INV(Random!D170,20,3),0))</f>
         <v>Enter your name</v>
       </c>
-      <c r="F54" s="65"/>
+      <c r="F54" s="149"/>
     </row>
     <row r="55" spans="3:6" ht="20.100000000000001" customHeight="1">
       <c r="C55" s="22">
@@ -5388,7 +5462,7 @@
         <f>IF(E$2="Your Name Here", "Enter your name",ROUND(_xlfn.NORM.INV(Random!D171,20,3),0))</f>
         <v>Enter your name</v>
       </c>
-      <c r="F55" s="65"/>
+      <c r="F55" s="149"/>
     </row>
     <row r="56" spans="3:6" ht="20.100000000000001" customHeight="1">
       <c r="C56" s="22">
@@ -5402,7 +5476,7 @@
         <f>IF(E$2="Your Name Here", "Enter your name",ROUND(_xlfn.NORM.INV(Random!D172,20,3),0))</f>
         <v>Enter your name</v>
       </c>
-      <c r="F56" s="65"/>
+      <c r="F56" s="149"/>
     </row>
     <row r="57" spans="3:6" ht="20.100000000000001" customHeight="1">
       <c r="C57" s="22">
@@ -5416,7 +5490,7 @@
         <f>IF(E$2="Your Name Here", "Enter your name",ROUND(_xlfn.NORM.INV(Random!D173,20,3),0))</f>
         <v>Enter your name</v>
       </c>
-      <c r="F57" s="65"/>
+      <c r="F57" s="149"/>
     </row>
     <row r="58" spans="3:6" ht="20.100000000000001" customHeight="1">
       <c r="C58" s="22">
@@ -5430,7 +5504,7 @@
         <f>IF(E$2="Your Name Here", "Enter your name",ROUND(_xlfn.NORM.INV(Random!D174,20,3),0))</f>
         <v>Enter your name</v>
       </c>
-      <c r="F58" s="65"/>
+      <c r="F58" s="149"/>
     </row>
     <row r="59" spans="3:6" ht="20.100000000000001" customHeight="1">
       <c r="C59" s="22">
@@ -5444,7 +5518,7 @@
         <f>IF(E$2="Your Name Here", "Enter your name",ROUND(_xlfn.NORM.INV(Random!D175,20,3),0))</f>
         <v>Enter your name</v>
       </c>
-      <c r="F59" s="65"/>
+      <c r="F59" s="149"/>
     </row>
     <row r="60" spans="3:6" ht="20.100000000000001" customHeight="1">
       <c r="C60" s="22">
@@ -5458,7 +5532,7 @@
         <f>IF(E$2="Your Name Here", "Enter your name",ROUND(_xlfn.NORM.INV(Random!D176,20,3),0))</f>
         <v>Enter your name</v>
       </c>
-      <c r="F60" s="65"/>
+      <c r="F60" s="149"/>
     </row>
     <row r="61" spans="3:6" ht="20.100000000000001" customHeight="1">
       <c r="C61" s="22">
@@ -5472,7 +5546,7 @@
         <f>IF(E$2="Your Name Here", "Enter your name",ROUND(_xlfn.NORM.INV(Random!D177,20,3),0))</f>
         <v>Enter your name</v>
       </c>
-      <c r="F61" s="65"/>
+      <c r="F61" s="149"/>
     </row>
     <row r="62" spans="3:6" ht="20.100000000000001" customHeight="1">
       <c r="C62" s="22">
@@ -5486,7 +5560,7 @@
         <f>IF(E$2="Your Name Here", "Enter your name",ROUND(_xlfn.NORM.INV(Random!D178,20,3),0))</f>
         <v>Enter your name</v>
       </c>
-      <c r="F62" s="65"/>
+      <c r="F62" s="149"/>
     </row>
     <row r="63" spans="3:6" ht="20.100000000000001" customHeight="1">
       <c r="C63" s="22">
@@ -5500,7 +5574,7 @@
         <f>IF(E$2="Your Name Here", "Enter your name",ROUND(_xlfn.NORM.INV(Random!D179,20,3),0))</f>
         <v>Enter your name</v>
       </c>
-      <c r="F63" s="65"/>
+      <c r="F63" s="149"/>
     </row>
     <row r="64" spans="3:6" ht="20.100000000000001" customHeight="1">
       <c r="C64" s="22">
@@ -5514,7 +5588,7 @@
         <f>IF(E$2="Your Name Here", "Enter your name",ROUND(_xlfn.NORM.INV(Random!D180,20,3),0))</f>
         <v>Enter your name</v>
       </c>
-      <c r="F64" s="65"/>
+      <c r="F64" s="149"/>
     </row>
     <row r="65" spans="3:6" ht="20.100000000000001" customHeight="1">
       <c r="C65" s="22">
@@ -5528,7 +5602,7 @@
         <f>IF(E$2="Your Name Here", "Enter your name",ROUND(_xlfn.NORM.INV(Random!D181,20,3),0))</f>
         <v>Enter your name</v>
       </c>
-      <c r="F65" s="65"/>
+      <c r="F65" s="149"/>
     </row>
     <row r="66" spans="3:6" ht="20.100000000000001" customHeight="1">
       <c r="C66" s="22">
@@ -5542,7 +5616,7 @@
         <f>IF(E$2="Your Name Here", "Enter your name",ROUND(_xlfn.NORM.INV(Random!D182,20,3),0))</f>
         <v>Enter your name</v>
       </c>
-      <c r="F66" s="65"/>
+      <c r="F66" s="149"/>
     </row>
     <row r="67" spans="3:6" ht="20.100000000000001" customHeight="1">
       <c r="C67" s="22">
@@ -5556,7 +5630,7 @@
         <f>IF(E$2="Your Name Here", "Enter your name",ROUND(_xlfn.NORM.INV(Random!D183,20,3),0))</f>
         <v>Enter your name</v>
       </c>
-      <c r="F67" s="65"/>
+      <c r="F67" s="149"/>
     </row>
     <row r="68" spans="3:6" ht="20.100000000000001" customHeight="1">
       <c r="C68" s="22">
@@ -5570,7 +5644,7 @@
         <f>IF(E$2="Your Name Here", "Enter your name",ROUND(_xlfn.NORM.INV(Random!D184,20,3),0))</f>
         <v>Enter your name</v>
       </c>
-      <c r="F68" s="65"/>
+      <c r="F68" s="149"/>
     </row>
     <row r="69" spans="3:6" ht="20.100000000000001" customHeight="1">
       <c r="C69" s="22">
@@ -5584,7 +5658,7 @@
         <f>IF(E$2="Your Name Here", "Enter your name",ROUND(_xlfn.NORM.INV(Random!D185,20,3),0))</f>
         <v>Enter your name</v>
       </c>
-      <c r="F69" s="65"/>
+      <c r="F69" s="149"/>
     </row>
     <row r="70" spans="3:6" ht="20.100000000000001" customHeight="1">
       <c r="C70" s="22">
@@ -5598,7 +5672,7 @@
         <f>IF(E$2="Your Name Here", "Enter your name",ROUND(_xlfn.NORM.INV(Random!D186,20,3),0))</f>
         <v>Enter your name</v>
       </c>
-      <c r="F70" s="65"/>
+      <c r="F70" s="149"/>
     </row>
     <row r="71" spans="3:6" ht="20.100000000000001" customHeight="1">
       <c r="C71" s="22">
@@ -5612,7 +5686,7 @@
         <f>IF(E$2="Your Name Here", "Enter your name",ROUND(_xlfn.NORM.INV(Random!D187,20,3),0))</f>
         <v>Enter your name</v>
       </c>
-      <c r="F71" s="65"/>
+      <c r="F71" s="149"/>
     </row>
     <row r="72" spans="3:6" ht="20.100000000000001" customHeight="1">
       <c r="C72" s="22">
@@ -5626,7 +5700,7 @@
         <f>IF(E$2="Your Name Here", "Enter your name",ROUND(_xlfn.NORM.INV(Random!D188,20,3),0))</f>
         <v>Enter your name</v>
       </c>
-      <c r="F72" s="65"/>
+      <c r="F72" s="149"/>
     </row>
     <row r="73" spans="3:6" ht="20.100000000000001" customHeight="1">
       <c r="C73" s="22">
@@ -5640,7 +5714,7 @@
         <f>IF(E$2="Your Name Here", "Enter your name",ROUND(_xlfn.NORM.INV(Random!D189,20,3),0))</f>
         <v>Enter your name</v>
       </c>
-      <c r="F73" s="65"/>
+      <c r="F73" s="149"/>
     </row>
     <row r="74" spans="3:6" ht="20.100000000000001" customHeight="1">
       <c r="C74" s="22">
@@ -5654,7 +5728,7 @@
         <f>IF(E$2="Your Name Here", "Enter your name",ROUND(_xlfn.NORM.INV(Random!D190,20,3),0))</f>
         <v>Enter your name</v>
       </c>
-      <c r="F74" s="65"/>
+      <c r="F74" s="149"/>
     </row>
     <row r="75" spans="3:6" ht="20.100000000000001" customHeight="1">
       <c r="C75" s="22">
@@ -5668,7 +5742,7 @@
         <f>IF(E$2="Your Name Here", "Enter your name",ROUND(_xlfn.NORM.INV(Random!D191,20,3),0))</f>
         <v>Enter your name</v>
       </c>
-      <c r="F75" s="65"/>
+      <c r="F75" s="149"/>
     </row>
     <row r="76" spans="3:6" ht="20.100000000000001" customHeight="1">
       <c r="C76" s="22">
@@ -5682,7 +5756,7 @@
         <f>IF(E$2="Your Name Here", "Enter your name",ROUND(_xlfn.NORM.INV(Random!D192,20,3),0))</f>
         <v>Enter your name</v>
       </c>
-      <c r="F76" s="65"/>
+      <c r="F76" s="149"/>
     </row>
     <row r="77" spans="3:6" ht="20.100000000000001" customHeight="1">
       <c r="C77" s="22">
@@ -5696,7 +5770,7 @@
         <f>IF(E$2="Your Name Here", "Enter your name",ROUND(_xlfn.NORM.INV(Random!D193,20,3),0))</f>
         <v>Enter your name</v>
       </c>
-      <c r="F77" s="65"/>
+      <c r="F77" s="149"/>
     </row>
     <row r="78" spans="3:6" ht="20.100000000000001" customHeight="1">
       <c r="C78" s="22">
@@ -5710,7 +5784,7 @@
         <f>IF(E$2="Your Name Here", "Enter your name",ROUND(_xlfn.NORM.INV(Random!D194,20,3),0))</f>
         <v>Enter your name</v>
       </c>
-      <c r="F78" s="65"/>
+      <c r="F78" s="149"/>
     </row>
     <row r="79" spans="3:6" ht="20.100000000000001" customHeight="1">
       <c r="C79" s="22">
@@ -5724,7 +5798,7 @@
         <f>IF(E$2="Your Name Here", "Enter your name",ROUND(_xlfn.NORM.INV(Random!D195,20,3),0))</f>
         <v>Enter your name</v>
       </c>
-      <c r="F79" s="65"/>
+      <c r="F79" s="149"/>
     </row>
     <row r="80" spans="3:6" ht="20.100000000000001" customHeight="1">
       <c r="C80" s="22">
@@ -5738,7 +5812,7 @@
         <f>IF(E$2="Your Name Here", "Enter your name",ROUND(_xlfn.NORM.INV(Random!D196,20,3),0))</f>
         <v>Enter your name</v>
       </c>
-      <c r="F80" s="65"/>
+      <c r="F80" s="149"/>
     </row>
     <row r="81" spans="3:6" ht="20.100000000000001" customHeight="1">
       <c r="C81" s="22">
@@ -5752,7 +5826,7 @@
         <f>IF(E$2="Your Name Here", "Enter your name",ROUND(_xlfn.NORM.INV(Random!D197,20,3),0))</f>
         <v>Enter your name</v>
       </c>
-      <c r="F81" s="65"/>
+      <c r="F81" s="149"/>
     </row>
     <row r="82" spans="3:6" ht="20.100000000000001" customHeight="1">
       <c r="C82" s="22">
@@ -5766,7 +5840,7 @@
         <f>IF(E$2="Your Name Here", "Enter your name",ROUND(_xlfn.NORM.INV(Random!D198,20,3),0))</f>
         <v>Enter your name</v>
       </c>
-      <c r="F82" s="65"/>
+      <c r="F82" s="149"/>
     </row>
     <row r="83" spans="3:6" ht="20.100000000000001" customHeight="1">
       <c r="C83" s="22">
@@ -5780,7 +5854,7 @@
         <f>IF(E$2="Your Name Here", "Enter your name",ROUND(_xlfn.NORM.INV(Random!D199,20,3),0))</f>
         <v>Enter your name</v>
       </c>
-      <c r="F83" s="65"/>
+      <c r="F83" s="149"/>
     </row>
     <row r="84" spans="3:6" ht="20.100000000000001" customHeight="1">
       <c r="C84" s="22">
@@ -5794,7 +5868,7 @@
         <f>IF(E$2="Your Name Here", "Enter your name",ROUND(_xlfn.NORM.INV(Random!D200,20,3),0))</f>
         <v>Enter your name</v>
       </c>
-      <c r="F84" s="65"/>
+      <c r="F84" s="149"/>
     </row>
     <row r="85" spans="3:6" ht="20.100000000000001" customHeight="1">
       <c r="C85" s="22">
@@ -5808,7 +5882,7 @@
         <f>IF(E$2="Your Name Here", "Enter your name",ROUND(_xlfn.NORM.INV(Random!D201,20,3),0))</f>
         <v>Enter your name</v>
       </c>
-      <c r="F85" s="65"/>
+      <c r="F85" s="149"/>
     </row>
     <row r="86" spans="3:6" ht="20.100000000000001" customHeight="1">
       <c r="C86" s="22">
@@ -5822,7 +5896,7 @@
         <f>IF(E$2="Your Name Here", "Enter your name",ROUND(_xlfn.NORM.INV(Random!D202,20,3),0))</f>
         <v>Enter your name</v>
       </c>
-      <c r="F86" s="65"/>
+      <c r="F86" s="149"/>
     </row>
     <row r="87" spans="3:6" ht="20.100000000000001" customHeight="1">
       <c r="C87" s="22">
@@ -5836,7 +5910,7 @@
         <f>IF(E$2="Your Name Here", "Enter your name",ROUND(_xlfn.NORM.INV(Random!D203,20,3),0))</f>
         <v>Enter your name</v>
       </c>
-      <c r="F87" s="65"/>
+      <c r="F87" s="149"/>
     </row>
     <row r="88" spans="3:6" ht="20.100000000000001" customHeight="1">
       <c r="C88" s="22">
@@ -5850,7 +5924,7 @@
         <f>IF(E$2="Your Name Here", "Enter your name",ROUND(_xlfn.NORM.INV(Random!D204,20,3),0))</f>
         <v>Enter your name</v>
       </c>
-      <c r="F88" s="65"/>
+      <c r="F88" s="149"/>
     </row>
     <row r="89" spans="3:6" ht="20.100000000000001" customHeight="1">
       <c r="C89" s="22">
@@ -5864,7 +5938,7 @@
         <f>IF(E$2="Your Name Here", "Enter your name",ROUND(_xlfn.NORM.INV(Random!D205,20,3),0))</f>
         <v>Enter your name</v>
       </c>
-      <c r="F89" s="65"/>
+      <c r="F89" s="149"/>
     </row>
     <row r="90" spans="3:6" ht="20.100000000000001" customHeight="1">
       <c r="C90" s="22">
@@ -5878,7 +5952,7 @@
         <f>IF(E$2="Your Name Here", "Enter your name",ROUND(_xlfn.NORM.INV(Random!D206,20,3),0))</f>
         <v>Enter your name</v>
       </c>
-      <c r="F90" s="65"/>
+      <c r="F90" s="149"/>
     </row>
     <row r="91" spans="3:6" ht="20.100000000000001" customHeight="1">
       <c r="C91" s="22">
@@ -5892,7 +5966,7 @@
         <f>IF(E$2="Your Name Here", "Enter your name",ROUND(_xlfn.NORM.INV(Random!D207,20,3),0))</f>
         <v>Enter your name</v>
       </c>
-      <c r="F91" s="65"/>
+      <c r="F91" s="149"/>
     </row>
     <row r="92" spans="3:6" ht="20.100000000000001" customHeight="1">
       <c r="C92" s="22">
@@ -5906,7 +5980,7 @@
         <f>IF(E$2="Your Name Here", "Enter your name",ROUND(_xlfn.NORM.INV(Random!D208,20,3),0))</f>
         <v>Enter your name</v>
       </c>
-      <c r="F92" s="65"/>
+      <c r="F92" s="149"/>
     </row>
     <row r="93" spans="3:6" ht="20.100000000000001" customHeight="1">
       <c r="C93" s="22">
@@ -5920,7 +5994,7 @@
         <f>IF(E$2="Your Name Here", "Enter your name",ROUND(_xlfn.NORM.INV(Random!D209,20,3),0))</f>
         <v>Enter your name</v>
       </c>
-      <c r="F93" s="65"/>
+      <c r="F93" s="149"/>
     </row>
     <row r="94" spans="3:6" ht="20.100000000000001" customHeight="1">
       <c r="C94" s="22">
@@ -5934,7 +6008,7 @@
         <f>IF(E$2="Your Name Here", "Enter your name",ROUND(_xlfn.NORM.INV(Random!D210,20,3),0))</f>
         <v>Enter your name</v>
       </c>
-      <c r="F94" s="65"/>
+      <c r="F94" s="149"/>
     </row>
     <row r="95" spans="3:6" ht="20.100000000000001" customHeight="1">
       <c r="C95" s="22">
@@ -5948,7 +6022,7 @@
         <f>IF(E$2="Your Name Here", "Enter your name",ROUND(_xlfn.NORM.INV(Random!D211,20,3),0))</f>
         <v>Enter your name</v>
       </c>
-      <c r="F95" s="65"/>
+      <c r="F95" s="149"/>
     </row>
     <row r="96" spans="3:6" ht="20.100000000000001" customHeight="1">
       <c r="C96" s="22">
@@ -5962,7 +6036,7 @@
         <f>IF(E$2="Your Name Here", "Enter your name",ROUND(_xlfn.NORM.INV(Random!D212,20,3),0))</f>
         <v>Enter your name</v>
       </c>
-      <c r="F96" s="65"/>
+      <c r="F96" s="149"/>
     </row>
     <row r="97" spans="3:6" ht="20.100000000000001" customHeight="1">
       <c r="C97" s="22">
@@ -5976,7 +6050,7 @@
         <f>IF(E$2="Your Name Here", "Enter your name",ROUND(_xlfn.NORM.INV(Random!D213,20,3),0))</f>
         <v>Enter your name</v>
       </c>
-      <c r="F97" s="65"/>
+      <c r="F97" s="149"/>
     </row>
     <row r="98" spans="3:6" ht="20.100000000000001" customHeight="1">
       <c r="C98" s="22">
@@ -5990,7 +6064,7 @@
         <f>IF(E$2="Your Name Here", "Enter your name",ROUND(_xlfn.NORM.INV(Random!D214,20,3),0))</f>
         <v>Enter your name</v>
       </c>
-      <c r="F98" s="65"/>
+      <c r="F98" s="149"/>
     </row>
     <row r="99" spans="3:6" ht="20.100000000000001" customHeight="1">
       <c r="C99" s="22">
@@ -6004,7 +6078,7 @@
         <f>IF(E$2="Your Name Here", "Enter your name",ROUND(_xlfn.NORM.INV(Random!D215,20,3),0))</f>
         <v>Enter your name</v>
       </c>
-      <c r="F99" s="65"/>
+      <c r="F99" s="149"/>
     </row>
     <row r="100" spans="3:6" ht="20.100000000000001" customHeight="1">
       <c r="C100" s="22">
@@ -6018,7 +6092,7 @@
         <f>IF(E$2="Your Name Here", "Enter your name",ROUND(_xlfn.NORM.INV(Random!D216,20,3),0))</f>
         <v>Enter your name</v>
       </c>
-      <c r="F100" s="65"/>
+      <c r="F100" s="149"/>
     </row>
     <row r="101" spans="3:6" ht="20.100000000000001" customHeight="1">
       <c r="C101" s="22">
@@ -6032,7 +6106,7 @@
         <f>IF(E$2="Your Name Here", "Enter your name",ROUND(_xlfn.NORM.INV(Random!D217,20,3),0))</f>
         <v>Enter your name</v>
       </c>
-      <c r="F101" s="65"/>
+      <c r="F101" s="149"/>
     </row>
     <row r="102" spans="3:6" ht="20.100000000000001" customHeight="1">
       <c r="C102" s="22">
@@ -6046,7 +6120,7 @@
         <f>IF(E$2="Your Name Here", "Enter your name",ROUND(_xlfn.NORM.INV(Random!D218,20,3),0))</f>
         <v>Enter your name</v>
       </c>
-      <c r="F102" s="65"/>
+      <c r="F102" s="149"/>
     </row>
     <row r="103" spans="3:6" ht="20.100000000000001" customHeight="1">
       <c r="C103" s="22">
@@ -6060,7 +6134,7 @@
         <f>IF(E$2="Your Name Here", "Enter your name",ROUND(_xlfn.NORM.INV(Random!D219,20,3),0))</f>
         <v>Enter your name</v>
       </c>
-      <c r="F103" s="65"/>
+      <c r="F103" s="149"/>
     </row>
     <row r="104" spans="3:6" ht="20.100000000000001" customHeight="1">
       <c r="C104" s="22">
@@ -6074,7 +6148,7 @@
         <f>IF(E$2="Your Name Here", "Enter your name",ROUND(_xlfn.NORM.INV(Random!D220,20,3),0))</f>
         <v>Enter your name</v>
       </c>
-      <c r="F104" s="65"/>
+      <c r="F104" s="149"/>
     </row>
     <row r="105" spans="3:6" ht="20.100000000000001" customHeight="1">
       <c r="C105" s="22">
@@ -6088,7 +6162,7 @@
         <f>IF(E$2="Your Name Here", "Enter your name",ROUND(_xlfn.NORM.INV(Random!D221,20,3),0))</f>
         <v>Enter your name</v>
       </c>
-      <c r="F105" s="65"/>
+      <c r="F105" s="149"/>
     </row>
     <row r="106" spans="3:6" ht="20.100000000000001" customHeight="1">
       <c r="C106" s="22">
@@ -6102,7 +6176,7 @@
         <f>IF(E$2="Your Name Here", "Enter your name",ROUND(_xlfn.NORM.INV(Random!D222,20,3),0))</f>
         <v>Enter your name</v>
       </c>
-      <c r="F106" s="65"/>
+      <c r="F106" s="149"/>
     </row>
     <row r="107" spans="3:6" ht="20.100000000000001" customHeight="1">
       <c r="C107" s="22">
@@ -6116,7 +6190,7 @@
         <f>IF(E$2="Your Name Here", "Enter your name",ROUND(_xlfn.NORM.INV(Random!D223,20,3),0))</f>
         <v>Enter your name</v>
       </c>
-      <c r="F107" s="65"/>
+      <c r="F107" s="149"/>
     </row>
     <row r="108" spans="3:6" ht="20.100000000000001" customHeight="1">
       <c r="C108" s="22">
@@ -6130,7 +6204,7 @@
         <f>IF(E$2="Your Name Here", "Enter your name",ROUND(_xlfn.NORM.INV(Random!D224,20,3),0))</f>
         <v>Enter your name</v>
       </c>
-      <c r="F108" s="65"/>
+      <c r="F108" s="149"/>
     </row>
     <row r="109" spans="3:6" ht="20.100000000000001" customHeight="1">
       <c r="C109" s="22">
@@ -6144,7 +6218,7 @@
         <f>IF(E$2="Your Name Here", "Enter your name",ROUND(_xlfn.NORM.INV(Random!D225,20,3),0))</f>
         <v>Enter your name</v>
       </c>
-      <c r="F109" s="65"/>
+      <c r="F109" s="149"/>
     </row>
     <row r="110" spans="3:6" ht="20.100000000000001" customHeight="1">
       <c r="C110" s="22">
@@ -6158,7 +6232,7 @@
         <f>IF(E$2="Your Name Here", "Enter your name",ROUND(_xlfn.NORM.INV(Random!D226,20,3),0))</f>
         <v>Enter your name</v>
       </c>
-      <c r="F110" s="65"/>
+      <c r="F110" s="149"/>
     </row>
     <row r="111" spans="3:6" ht="20.100000000000001" customHeight="1">
       <c r="C111" s="22">
@@ -6172,7 +6246,7 @@
         <f>IF(E$2="Your Name Here", "Enter your name",ROUND(_xlfn.NORM.INV(Random!D227,20,3),0))</f>
         <v>Enter your name</v>
       </c>
-      <c r="F111" s="65"/>
+      <c r="F111" s="149"/>
     </row>
     <row r="112" spans="3:6" ht="20.100000000000001" customHeight="1">
       <c r="C112" s="22">
@@ -6186,7 +6260,7 @@
         <f>IF(E$2="Your Name Here", "Enter your name",ROUND(_xlfn.NORM.INV(Random!D228,20,3),0))</f>
         <v>Enter your name</v>
       </c>
-      <c r="F112" s="65"/>
+      <c r="F112" s="149"/>
     </row>
     <row r="113" spans="3:6" ht="20.100000000000001" customHeight="1">
       <c r="C113" s="22">
@@ -6200,7 +6274,7 @@
         <f>IF(E$2="Your Name Here", "Enter your name",ROUND(_xlfn.NORM.INV(Random!D229,20,3),0))</f>
         <v>Enter your name</v>
       </c>
-      <c r="F113" s="65"/>
+      <c r="F113" s="149"/>
     </row>
     <row r="114" spans="3:6" ht="20.100000000000001" customHeight="1">
       <c r="C114" s="22">
@@ -6214,7 +6288,7 @@
         <f>IF(E$2="Your Name Here", "Enter your name",ROUND(_xlfn.NORM.INV(Random!D230,20,3),0))</f>
         <v>Enter your name</v>
       </c>
-      <c r="F114" s="65"/>
+      <c r="F114" s="149"/>
     </row>
     <row r="115" spans="3:6" ht="20.100000000000001" customHeight="1">
       <c r="C115" s="22">
@@ -6228,7 +6302,7 @@
         <f>IF(E$2="Your Name Here", "Enter your name",ROUND(_xlfn.NORM.INV(Random!D231,20,3),0))</f>
         <v>Enter your name</v>
       </c>
-      <c r="F115" s="65"/>
+      <c r="F115" s="149"/>
     </row>
     <row r="116" spans="3:6" ht="20.100000000000001" customHeight="1">
       <c r="C116" s="22">
@@ -6242,7 +6316,7 @@
         <f>IF(E$2="Your Name Here", "Enter your name",ROUND(_xlfn.NORM.INV(Random!D232,20,3),0))</f>
         <v>Enter your name</v>
       </c>
-      <c r="F116" s="65"/>
+      <c r="F116" s="149"/>
     </row>
     <row r="117" spans="3:6" ht="20.100000000000001" customHeight="1">
       <c r="C117" s="22">
@@ -6256,7 +6330,7 @@
         <f>IF(E$2="Your Name Here", "Enter your name",ROUND(_xlfn.NORM.INV(Random!D233,20,3),0))</f>
         <v>Enter your name</v>
       </c>
-      <c r="F117" s="65"/>
+      <c r="F117" s="149"/>
     </row>
     <row r="118" spans="3:6" ht="20.100000000000001" customHeight="1">
       <c r="C118" s="22">
@@ -6270,7 +6344,7 @@
         <f>IF(E$2="Your Name Here", "Enter your name",ROUND(_xlfn.NORM.INV(Random!D234,20,3),0))</f>
         <v>Enter your name</v>
       </c>
-      <c r="F118" s="65"/>
+      <c r="F118" s="149"/>
     </row>
     <row r="119" spans="3:6" ht="20.100000000000001" customHeight="1">
       <c r="C119" s="22">
@@ -6284,7 +6358,7 @@
         <f>IF(E$2="Your Name Here", "Enter your name",ROUND(_xlfn.NORM.INV(Random!D235,20,3),0))</f>
         <v>Enter your name</v>
       </c>
-      <c r="F119" s="65"/>
+      <c r="F119" s="149"/>
     </row>
     <row r="120" spans="3:6" ht="20.100000000000001" customHeight="1">
       <c r="C120" s="22">
@@ -6298,15 +6372,15 @@
         <f>IF(E$2="Your Name Here", "Enter your name",ROUND(_xlfn.NORM.INV(Random!D236,20,3),0))</f>
         <v>Enter your name</v>
       </c>
-      <c r="F120" s="65"/>
+      <c r="F120" s="149"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="XExoNlnWnvlMbBUPOfcysJUBNBnk3fGFRb/xwOKqnlB11MMI3BjhGo0WUxp5kBMheL+mH1Zj/n9NyJzBukk1pg==" saltValue="Wmj8tDNIvZvV6CBee4LS9Q==" spinCount="100000" sheet="1" formatCells="0" formatColumns="0" formatRows="0"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="c1/5b27c2dd+D5JIA2z+530aI04+n19uIbyDnAPnYY8kt6mlUCBWbrP8TYcpX9oO/vx3w4B7B+M3A55Zxq9VuA==" saltValue="v3/YkLBADXqOrIuk3+deTw==" spinCount="100000" sheet="1" formatCells="0" formatColumns="0" formatRows="0"/>
   <protectedRanges>
     <protectedRange sqref="E2" name="Range1_1"/>
     <protectedRange sqref="I19:I20" name="Range4_1"/>
   </protectedRanges>
-  <mergeCells count="12">
+  <mergeCells count="13">
     <mergeCell ref="J19:K20"/>
     <mergeCell ref="H25:P26"/>
     <mergeCell ref="C2:D2"/>
@@ -6319,6 +6393,7 @@
     <mergeCell ref="N12:Q12"/>
     <mergeCell ref="N14:Q14"/>
     <mergeCell ref="N15:Q15"/>
+    <mergeCell ref="M3:N3"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="custom" errorStyle="warning" allowBlank="1" showErrorMessage="1" error="A correct Excel formula must be used here." prompt="An Excel formula is required." sqref="F121:F1002 I4:I8" xr:uid="{F7FF74B4-2758-4A2A-944E-E148ECCE6B40}">
@@ -6328,8 +6403,12 @@
       <formula1>$K$29:$K$31</formula1>
     </dataValidation>
   </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="M3:N3" r:id="rId1" display="Video" xr:uid="{CFDAE263-4CA4-478F-9920-E6D696F0B92E}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId2"/>
+  <legacyDrawing r:id="rId3"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
@@ -6344,7 +6423,7 @@
               </font>
             </x14:dxf>
           </x14:cfRule>
-          <xm:sqref>F4:F120 I9:K10 I12:K12 I28 K28 M28 O28</xm:sqref>
+          <xm:sqref>I28 K28 M28 O28 F4:F120 I9:K10 I12:K12</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="expression" priority="3" id="{7FB5BF67-D3C9-433F-8BD1-7A1A43069998}">
@@ -6375,7 +6454,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <xm:sqref>I9:K12 F4:F120 I28 M28 O28 I19:I20</xm:sqref>
+          <xm:sqref>I28 M28 O28 I19:I20 F4:F120 I9:K12</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="expression" priority="5" id="{277BB918-2059-4665-8CEA-40B8AA909FC2}">
@@ -6437,24 +6516,24 @@
       <c r="F1" s="1"/>
     </row>
     <row r="2" spans="3:26" ht="61.9" customHeight="1" thickBot="1">
-      <c r="C2" s="128" t="s">
+      <c r="C2" s="121" t="s">
         <v>42</v>
       </c>
-      <c r="D2" s="129"/>
+      <c r="D2" s="122"/>
       <c r="E2" s="26" t="str">
         <f>Improvement!E2</f>
         <v>Your Name Here</v>
       </c>
-      <c r="F2" s="130" t="s">
+      <c r="F2" s="123" t="s">
         <v>10</v>
       </c>
-      <c r="G2" s="131"/>
-      <c r="H2" s="131"/>
-      <c r="I2" s="131"/>
-      <c r="J2" s="131"/>
-      <c r="K2" s="131"/>
-      <c r="L2" s="131"/>
-      <c r="M2" s="131"/>
+      <c r="G2" s="124"/>
+      <c r="H2" s="124"/>
+      <c r="I2" s="124"/>
+      <c r="J2" s="124"/>
+      <c r="K2" s="124"/>
+      <c r="L2" s="124"/>
+      <c r="M2" s="124"/>
       <c r="N2" s="16"/>
       <c r="O2" s="16"/>
       <c r="P2" s="16"/>
@@ -6482,17 +6561,17 @@
         <v>14</v>
       </c>
       <c r="G3" s="25"/>
-      <c r="H3" s="132" t="s">
+      <c r="H3" s="125" t="s">
         <v>43</v>
       </c>
-      <c r="I3" s="133"/>
-      <c r="J3" s="133"/>
-      <c r="K3" s="134"/>
-      <c r="L3" s="75"/>
-      <c r="M3" s="75"/>
-      <c r="N3" s="76"/>
-      <c r="O3" s="76"/>
-      <c r="P3" s="76"/>
+      <c r="I3" s="126"/>
+      <c r="J3" s="126"/>
+      <c r="K3" s="127"/>
+      <c r="L3" s="68"/>
+      <c r="M3" s="68"/>
+      <c r="N3" s="69"/>
+      <c r="O3" s="69"/>
+      <c r="P3" s="69"/>
       <c r="Q3" s="16"/>
       <c r="R3" s="16"/>
       <c r="S3" s="16"/>
@@ -6526,15 +6605,15 @@
 TRUE)</f>
         <v>1</v>
       </c>
-      <c r="H4" s="135"/>
-      <c r="I4" s="136"/>
-      <c r="J4" s="136"/>
-      <c r="K4" s="137"/>
-      <c r="L4" s="79"/>
-      <c r="M4" s="79"/>
-      <c r="N4" s="77"/>
-      <c r="O4" s="78"/>
-      <c r="P4" s="78"/>
+      <c r="H4" s="128"/>
+      <c r="I4" s="129"/>
+      <c r="J4" s="129"/>
+      <c r="K4" s="130"/>
+      <c r="L4" s="72"/>
+      <c r="M4" s="72"/>
+      <c r="N4" s="70"/>
+      <c r="O4" s="71"/>
+      <c r="P4" s="71"/>
     </row>
     <row r="5" spans="3:26" ht="15" customHeight="1">
       <c r="C5" s="22">
@@ -6556,15 +6635,15 @@
         <f t="array" ref="G5">AND(AND(_xlfn.ISFORMULA(Improvement!F4:F120)),AND(Improvement!F4:F120=Soln!F4:F120))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="H5" s="135"/>
-      <c r="I5" s="136"/>
-      <c r="J5" s="136"/>
-      <c r="K5" s="137"/>
-      <c r="L5" s="79"/>
-      <c r="M5" s="79"/>
-      <c r="N5" s="76"/>
-      <c r="O5" s="76"/>
-      <c r="P5" s="76"/>
+      <c r="H5" s="128"/>
+      <c r="I5" s="129"/>
+      <c r="J5" s="129"/>
+      <c r="K5" s="130"/>
+      <c r="L5" s="72"/>
+      <c r="M5" s="72"/>
+      <c r="N5" s="69"/>
+      <c r="O5" s="69"/>
+      <c r="P5" s="69"/>
       <c r="Q5" s="16"/>
       <c r="R5" s="16"/>
       <c r="S5" s="16"/>
@@ -6591,18 +6670,18 @@
         <f>E6-D6</f>
         <v>#VALUE!</v>
       </c>
-      <c r="H6" s="135"/>
-      <c r="I6" s="136"/>
-      <c r="J6" s="136"/>
-      <c r="K6" s="137"/>
-      <c r="L6" s="79"/>
-      <c r="M6" s="79" t="b" cm="1">
+      <c r="H6" s="128"/>
+      <c r="I6" s="129"/>
+      <c r="J6" s="129"/>
+      <c r="K6" s="130"/>
+      <c r="L6" s="72"/>
+      <c r="M6" s="72" t="b" cm="1">
         <f t="array" aca="1" ref="M6" ca="1">IFERROR(STRIP(Improvement!F4)&lt;&gt;"=E4:E120-D4:D120",TRUE)</f>
         <v>1</v>
       </c>
-      <c r="N6" s="76"/>
-      <c r="O6" s="76"/>
-      <c r="P6" s="76"/>
+      <c r="N6" s="69"/>
+      <c r="O6" s="69"/>
+      <c r="P6" s="69"/>
       <c r="Q6" s="16"/>
       <c r="R6" s="16"/>
       <c r="S6" s="16"/>
@@ -6629,15 +6708,15 @@
         <f>E7-D7</f>
         <v>#VALUE!</v>
       </c>
-      <c r="H7" s="138"/>
-      <c r="I7" s="136"/>
-      <c r="J7" s="136"/>
-      <c r="K7" s="137"/>
-      <c r="L7" s="78"/>
-      <c r="M7" s="78"/>
-      <c r="N7" s="76"/>
-      <c r="O7" s="76"/>
-      <c r="P7" s="76"/>
+      <c r="H7" s="131"/>
+      <c r="I7" s="129"/>
+      <c r="J7" s="129"/>
+      <c r="K7" s="130"/>
+      <c r="L7" s="71"/>
+      <c r="M7" s="71"/>
+      <c r="N7" s="69"/>
+      <c r="O7" s="69"/>
+      <c r="P7" s="69"/>
       <c r="Q7" s="16"/>
       <c r="R7" s="16"/>
       <c r="S7" s="16"/>
@@ -6674,11 +6753,11 @@
       <c r="K8" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="L8" s="78"/>
-      <c r="M8" s="78"/>
-      <c r="N8" s="76"/>
-      <c r="O8" s="76"/>
-      <c r="P8" s="76"/>
+      <c r="L8" s="71"/>
+      <c r="M8" s="71"/>
+      <c r="N8" s="69"/>
+      <c r="O8" s="69"/>
+      <c r="P8" s="69"/>
       <c r="Q8" s="16"/>
       <c r="R8" s="16"/>
       <c r="S8" s="16"/>
@@ -6718,11 +6797,11 @@
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
-      <c r="L9" s="78"/>
-      <c r="M9" s="78"/>
-      <c r="N9" s="76"/>
-      <c r="O9" s="76"/>
-      <c r="P9" s="76"/>
+      <c r="L9" s="71"/>
+      <c r="M9" s="71"/>
+      <c r="N9" s="69"/>
+      <c r="O9" s="69"/>
+      <c r="P9" s="69"/>
       <c r="Q9" s="16"/>
       <c r="R9" s="16"/>
       <c r="S9" s="16"/>
@@ -6762,11 +6841,11 @@
         <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
-      <c r="L10" s="78"/>
-      <c r="M10" s="78"/>
-      <c r="N10" s="76"/>
-      <c r="O10" s="76"/>
-      <c r="P10" s="76"/>
+      <c r="L10" s="71"/>
+      <c r="M10" s="71"/>
+      <c r="N10" s="69"/>
+      <c r="O10" s="69"/>
+      <c r="P10" s="69"/>
       <c r="Q10" s="16"/>
       <c r="R10" s="16"/>
       <c r="S10" s="16"/>
@@ -6806,20 +6885,20 @@
         <f t="shared" si="3"/>
         <v>#VALUE!</v>
       </c>
-      <c r="L11" s="78" t="e">
+      <c r="L11" s="71" t="e">
         <f>_xlfn.STDEV.P(D4:D120)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="M11" s="78" t="e">
+      <c r="M11" s="71" t="e">
         <f t="shared" ref="M11:N11" si="4">_xlfn.STDEV.P(E4:E120)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="N11" s="78" t="e">
+      <c r="N11" s="71" t="e">
         <f t="shared" si="4"/>
         <v>#VALUE!</v>
       </c>
-      <c r="O11" s="78"/>
-      <c r="P11" s="76"/>
+      <c r="O11" s="71"/>
+      <c r="P11" s="69"/>
       <c r="Q11" s="16"/>
       <c r="R11" s="16"/>
       <c r="S11" s="16"/>
@@ -6932,12 +7011,12 @@
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
-      <c r="H15" s="132" t="s">
+      <c r="H15" s="125" t="s">
         <v>36</v>
       </c>
-      <c r="I15" s="133"/>
-      <c r="J15" s="133"/>
-      <c r="K15" s="134"/>
+      <c r="I15" s="126"/>
+      <c r="J15" s="126"/>
+      <c r="K15" s="127"/>
       <c r="L15" s="16"/>
       <c r="M15" s="16"/>
       <c r="N15" s="16"/>
@@ -6967,10 +7046,10 @@
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
-      <c r="H16" s="135"/>
-      <c r="I16" s="136"/>
-      <c r="J16" s="136"/>
-      <c r="K16" s="137"/>
+      <c r="H16" s="128"/>
+      <c r="I16" s="129"/>
+      <c r="J16" s="129"/>
+      <c r="K16" s="130"/>
       <c r="L16" s="16"/>
       <c r="M16" s="16"/>
       <c r="N16" s="16"/>
@@ -7000,10 +7079,10 @@
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
-      <c r="H17" s="135"/>
-      <c r="I17" s="136"/>
-      <c r="J17" s="139"/>
-      <c r="K17" s="140"/>
+      <c r="H17" s="128"/>
+      <c r="I17" s="129"/>
+      <c r="J17" s="132"/>
+      <c r="K17" s="133"/>
       <c r="L17" s="16"/>
       <c r="M17" s="16"/>
       <c r="N17" s="16"/>
@@ -7033,10 +7112,10 @@
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
-      <c r="H18" s="141" t="s">
+      <c r="H18" s="134" t="s">
         <v>38</v>
       </c>
-      <c r="I18" s="142"/>
+      <c r="I18" s="135"/>
       <c r="J18" s="18"/>
       <c r="K18" s="18"/>
       <c r="L18" s="16"/>
@@ -7266,17 +7345,17 @@
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
-      <c r="H25" s="102" t="s">
+      <c r="H25" s="95" t="s">
         <v>510</v>
       </c>
-      <c r="I25" s="103"/>
-      <c r="J25" s="103"/>
-      <c r="K25" s="103"/>
-      <c r="L25" s="103"/>
-      <c r="M25" s="103"/>
-      <c r="N25" s="103"/>
-      <c r="O25" s="103"/>
-      <c r="P25" s="104"/>
+      <c r="I25" s="96"/>
+      <c r="J25" s="96"/>
+      <c r="K25" s="96"/>
+      <c r="L25" s="96"/>
+      <c r="M25" s="96"/>
+      <c r="N25" s="96"/>
+      <c r="O25" s="96"/>
+      <c r="P25" s="97"/>
       <c r="Q25" s="17"/>
       <c r="R25" s="17"/>
       <c r="S25" s="17"/>
@@ -7299,15 +7378,15 @@
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
-      <c r="H26" s="105"/>
-      <c r="I26" s="106"/>
-      <c r="J26" s="106"/>
-      <c r="K26" s="106"/>
-      <c r="L26" s="106"/>
-      <c r="M26" s="106"/>
-      <c r="N26" s="106"/>
-      <c r="O26" s="106"/>
-      <c r="P26" s="107"/>
+      <c r="H26" s="98"/>
+      <c r="I26" s="99"/>
+      <c r="J26" s="99"/>
+      <c r="K26" s="99"/>
+      <c r="L26" s="99"/>
+      <c r="M26" s="99"/>
+      <c r="N26" s="99"/>
+      <c r="O26" s="99"/>
+      <c r="P26" s="100"/>
       <c r="Q26" s="17"/>
       <c r="R26" s="17"/>
       <c r="S26" s="17"/>
@@ -7386,14 +7465,14 @@
       <c r="L28" s="63" t="s">
         <v>503</v>
       </c>
-      <c r="M28" s="73" t="e">
+      <c r="M28" s="66" t="e">
         <f>K9-K11</f>
         <v>#VALUE!</v>
       </c>
       <c r="N28" s="63" t="s">
         <v>505</v>
       </c>
-      <c r="O28" s="73" t="e">
+      <c r="O28" s="66" t="e">
         <f>K9+K11</f>
         <v>#VALUE!</v>
       </c>
@@ -7428,12 +7507,12 @@
         <v>502</v>
       </c>
       <c r="L29" s="56"/>
-      <c r="M29" s="74" t="e">
+      <c r="M29" s="67" t="e">
         <f>K9-N11</f>
         <v>#VALUE!</v>
       </c>
       <c r="N29" s="56"/>
-      <c r="O29" s="74" t="e">
+      <c r="O29" s="67" t="e">
         <f>K9+N11</f>
         <v>#VALUE!</v>
       </c>
@@ -7621,9 +7700,9 @@
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
-      <c r="N35" s="127"/>
-      <c r="O35" s="127"/>
-      <c r="P35" s="127"/>
+      <c r="N35" s="120"/>
+      <c r="O35" s="120"/>
+      <c r="P35" s="120"/>
     </row>
     <row r="36" spans="3:25" ht="15.75">
       <c r="C36" s="22">
@@ -9206,17 +9285,17 @@
     <mergeCell ref="H25:P26"/>
   </mergeCells>
   <conditionalFormatting sqref="D4:E1002">
-    <cfRule type="expression" dxfId="2" priority="3">
+    <cfRule type="expression" dxfId="4" priority="3">
       <formula>ISNA(D4)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F121:F1002">
-    <cfRule type="expression" dxfId="1" priority="2">
+    <cfRule type="expression" dxfId="3" priority="2">
       <formula>AND(OR(ISBLANK(F121),F121="formula"),ISNUMBER(E121))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I4:I8">
-    <cfRule type="expression" dxfId="0" priority="1">
+    <cfRule type="expression" dxfId="2" priority="1">
       <formula>OR(ISBLANK(I4),I4="formula")</formula>
     </cfRule>
   </conditionalFormatting>
@@ -19719,69 +19798,69 @@
   <sheetData>
     <row r="1" spans="2:8" ht="15.75" thickBot="1"/>
     <row r="2" spans="2:8">
-      <c r="B2" s="143" t="s">
+      <c r="B2" s="136" t="s">
         <v>495</v>
       </c>
-      <c r="C2" s="144"/>
-      <c r="D2" s="144"/>
-      <c r="E2" s="144"/>
-      <c r="F2" s="144"/>
-      <c r="G2" s="144"/>
-      <c r="H2" s="145"/>
+      <c r="C2" s="137"/>
+      <c r="D2" s="137"/>
+      <c r="E2" s="137"/>
+      <c r="F2" s="137"/>
+      <c r="G2" s="137"/>
+      <c r="H2" s="138"/>
     </row>
     <row r="3" spans="2:8">
-      <c r="B3" s="146"/>
-      <c r="C3" s="147"/>
-      <c r="D3" s="147"/>
-      <c r="E3" s="147"/>
-      <c r="F3" s="147"/>
-      <c r="G3" s="147"/>
-      <c r="H3" s="148"/>
+      <c r="B3" s="139"/>
+      <c r="C3" s="140"/>
+      <c r="D3" s="140"/>
+      <c r="E3" s="140"/>
+      <c r="F3" s="140"/>
+      <c r="G3" s="140"/>
+      <c r="H3" s="141"/>
     </row>
     <row r="4" spans="2:8">
-      <c r="B4" s="146"/>
-      <c r="C4" s="147"/>
-      <c r="D4" s="147"/>
-      <c r="E4" s="147"/>
-      <c r="F4" s="147"/>
-      <c r="G4" s="147"/>
-      <c r="H4" s="148"/>
+      <c r="B4" s="139"/>
+      <c r="C4" s="140"/>
+      <c r="D4" s="140"/>
+      <c r="E4" s="140"/>
+      <c r="F4" s="140"/>
+      <c r="G4" s="140"/>
+      <c r="H4" s="141"/>
     </row>
     <row r="5" spans="2:8">
-      <c r="B5" s="146"/>
-      <c r="C5" s="147"/>
-      <c r="D5" s="147"/>
-      <c r="E5" s="147"/>
-      <c r="F5" s="147"/>
-      <c r="G5" s="147"/>
-      <c r="H5" s="148"/>
+      <c r="B5" s="139"/>
+      <c r="C5" s="140"/>
+      <c r="D5" s="140"/>
+      <c r="E5" s="140"/>
+      <c r="F5" s="140"/>
+      <c r="G5" s="140"/>
+      <c r="H5" s="141"/>
     </row>
     <row r="6" spans="2:8">
-      <c r="B6" s="146"/>
-      <c r="C6" s="147"/>
-      <c r="D6" s="147"/>
-      <c r="E6" s="147"/>
-      <c r="F6" s="147"/>
-      <c r="G6" s="147"/>
-      <c r="H6" s="148"/>
+      <c r="B6" s="139"/>
+      <c r="C6" s="140"/>
+      <c r="D6" s="140"/>
+      <c r="E6" s="140"/>
+      <c r="F6" s="140"/>
+      <c r="G6" s="140"/>
+      <c r="H6" s="141"/>
     </row>
     <row r="7" spans="2:8">
-      <c r="B7" s="146"/>
-      <c r="C7" s="147"/>
-      <c r="D7" s="147"/>
-      <c r="E7" s="147"/>
-      <c r="F7" s="147"/>
-      <c r="G7" s="147"/>
-      <c r="H7" s="148"/>
+      <c r="B7" s="139"/>
+      <c r="C7" s="140"/>
+      <c r="D7" s="140"/>
+      <c r="E7" s="140"/>
+      <c r="F7" s="140"/>
+      <c r="G7" s="140"/>
+      <c r="H7" s="141"/>
     </row>
     <row r="8" spans="2:8" ht="15.75" thickBot="1">
-      <c r="B8" s="149"/>
-      <c r="C8" s="150"/>
-      <c r="D8" s="150"/>
-      <c r="E8" s="150"/>
-      <c r="F8" s="150"/>
-      <c r="G8" s="150"/>
-      <c r="H8" s="151"/>
+      <c r="B8" s="142"/>
+      <c r="C8" s="143"/>
+      <c r="D8" s="143"/>
+      <c r="E8" s="143"/>
+      <c r="F8" s="143"/>
+      <c r="G8" s="143"/>
+      <c r="H8" s="144"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -19793,18 +19872,17 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="cca9fd2d-ef84-45c9-8063-8f4bd4c29606">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101002C289946819CFF499E91D197BC975371" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="42fa38ab43a81509e346454549077e6d">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="cca9fd2d-ef84-45c9-8063-8f4bd4c29606" xmlns:ns3="18557d39-01b8-4d71-9479-3fad465290ae" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4c114411e421f950bcfed138b48f6b8f" ns2:_="" ns3:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101002C289946819CFF499E91D197BC975371" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="674b7a4e239a9748c7aaa97e309327a4">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="cca9fd2d-ef84-45c9-8063-8f4bd4c29606" xmlns:ns3="18557d39-01b8-4d71-9479-3fad465290ae" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="600253478e594d1349e02792803dc53a" ns2:_="" ns3:_="">
     <xsd:import namespace="cca9fd2d-ef84-45c9-8063-8f4bd4c29606"/>
     <xsd:import namespace="18557d39-01b8-4d71-9479-3fad465290ae"/>
     <xsd:element name="properties">
@@ -20020,15 +20098,28 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="cca9fd2d-ef84-45c9-8063-8f4bd4c29606">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D86DD8B2-DEEC-4E06-8457-41AAA301C970}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BC767FF-5A74-4602-9BD9-BEBFFC59830D}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3F8E2865-77DA-4E6C-B7B7-F28C767E6578}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -20036,31 +20127,4 @@
     <ds:schemaRef ds:uri="cca9fd2d-ef84-45c9-8063-8f4bd4c29606"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CC18042D-4B6D-4EEE-85E6-34F4E0DB84BD}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="cca9fd2d-ef84-45c9-8063-8f4bd4c29606"/>
-    <ds:schemaRef ds:uri="18557d39-01b8-4d71-9479-3fad465290ae"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D86DD8B2-DEEC-4E06-8457-41AAA301C970}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>